--- a/data/excel/Polla Mundialista Final MAYALA.xlsx
+++ b/data/excel/Polla Mundialista Final MAYALA.xlsx
@@ -1,27 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="27510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scordova/Desktop/Polla Mundialista/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jose/Documents/ProyectoPollaMundiailista/data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6115A20-2816-B04A-9CB5-5ECF18402FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500"/>
   </bookViews>
   <sheets>
     <sheet name="POLLA FINAL" sheetId="1" r:id="rId1"/>
     <sheet name="Reglas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="269">
   <si>
     <t>POLLA PARA EL MUNDIAL MEXICO  CANADA USA 2026</t>
   </si>
@@ -886,7 +893,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm/dd"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
@@ -2138,31 +2145,23 @@
     <xf numFmtId="0" fontId="41" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2173,48 +2172,67 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="35" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="36" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2235,38 +2253,27 @@
     <xf numFmtId="0" fontId="38" fillId="26" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="34" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="35" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="50">
@@ -2898,7 +2905,7 @@
         <xdr:cNvPr id="2" name="Shape 2" title="Drawing">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2917,7 +2924,7 @@
           <xdr:cNvPr id="3" name="Shape 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2959,7 +2966,7 @@
         <xdr:cNvPr id="4" name="Shape 2" title="Drawing">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2978,7 +2985,7 @@
           <xdr:cNvPr id="5" name="Shape 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000005000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3025,7 +3032,7 @@
         <xdr:cNvPr id="2" name="image1.png" title="Image">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3246,8 +3253,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AI74"/>
@@ -3290,80 +3297,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
-      <c r="AC1" s="107"/>
-      <c r="AD1" s="107"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="105"/>
+      <c r="AC1" s="105"/>
+      <c r="AD1" s="105"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
       <c r="AI1" s="2"/>
     </row>
     <row r="2" spans="1:35" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="113" t="s">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="108" t="s">
         <v>267</v>
       </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="112" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="107"/>
+      <c r="P2" s="105"/>
       <c r="Q2" s="3"/>
-      <c r="R2" s="113">
+      <c r="R2" s="108">
         <v>968878857</v>
       </c>
-      <c r="S2" s="107"/>
-      <c r="T2" s="107"/>
-      <c r="U2" s="107"/>
-      <c r="V2" s="107"/>
-      <c r="W2" s="107"/>
-      <c r="X2" s="112" t="s">
+      <c r="S2" s="105"/>
+      <c r="T2" s="105"/>
+      <c r="U2" s="105"/>
+      <c r="V2" s="105"/>
+      <c r="W2" s="105"/>
+      <c r="X2" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="107"/>
-      <c r="Z2" s="107"/>
-      <c r="AA2" s="156" t="s">
+      <c r="Y2" s="105"/>
+      <c r="Z2" s="105"/>
+      <c r="AA2" s="103" t="s">
         <v>268</v>
       </c>
       <c r="AB2" s="4"/>
@@ -3376,13 +3383,13 @@
       <c r="AI2" s="7"/>
     </row>
     <row r="3" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="114" t="s">
+      <c r="A3" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="116"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="112"/>
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
       <c r="H3" s="10"/>
@@ -3415,11 +3422,11 @@
       <c r="AI3" s="14"/>
     </row>
     <row r="4" spans="1:35" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="119"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="115"/>
       <c r="F4" s="15"/>
       <c r="G4" s="16"/>
       <c r="H4" s="17"/>
@@ -3552,7 +3559,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="30"/>
-      <c r="G7" s="120" t="s">
+      <c r="G7" s="104" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="32" t="s">
@@ -3609,11 +3616,13 @@
         <v>3</v>
       </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="107"/>
+      <c r="G8" s="105"/>
       <c r="H8" s="23"/>
       <c r="I8" s="34"/>
       <c r="J8" s="35"/>
-      <c r="K8" s="33"/>
+      <c r="K8" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="L8" s="36"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -3627,7 +3636,9 @@
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8" s="33"/>
+      <c r="AA8" s="33" t="s">
+        <v>27</v>
+      </c>
       <c r="AB8" s="35"/>
       <c r="AC8" s="37"/>
       <c r="AD8" s="38"/>
@@ -3650,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="30"/>
-      <c r="G9" s="107"/>
+      <c r="G9" s="105"/>
       <c r="H9" s="39" t="s">
         <v>260</v>
       </c>
@@ -3697,13 +3708,15 @@
       <c r="D10" s="44"/>
       <c r="E10" s="44"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="107"/>
+      <c r="G10" s="105"/>
       <c r="H10" s="23"/>
       <c r="I10" s="36"/>
       <c r="J10" s="1"/>
       <c r="K10" s="45"/>
       <c r="L10" s="46"/>
-      <c r="M10" s="33"/>
+      <c r="M10" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -3715,7 +3728,9 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="33"/>
+      <c r="Y10" s="33" t="s">
+        <v>27</v>
+      </c>
       <c r="Z10" s="46"/>
       <c r="AA10" s="47"/>
       <c r="AB10" s="1"/>
@@ -3742,7 +3757,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="13"/>
-      <c r="G11" s="107"/>
+      <c r="G11" s="105"/>
       <c r="H11" s="32" t="s">
         <v>25</v>
       </c>
@@ -3797,11 +3812,13 @@
         <v>1</v>
       </c>
       <c r="F12" s="13"/>
-      <c r="G12" s="107"/>
+      <c r="G12" s="105"/>
       <c r="H12" s="23"/>
       <c r="I12" s="34"/>
       <c r="J12" s="35"/>
-      <c r="K12" s="33"/>
+      <c r="K12" s="33" t="s">
+        <v>76</v>
+      </c>
       <c r="L12" s="36"/>
       <c r="M12" s="40"/>
       <c r="N12" s="1"/>
@@ -3815,7 +3832,9 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="41"/>
       <c r="Z12" s="36"/>
-      <c r="AA12" s="33"/>
+      <c r="AA12" s="33" t="s">
+        <v>43</v>
+      </c>
       <c r="AB12" s="35"/>
       <c r="AC12" s="37"/>
       <c r="AD12" s="23"/>
@@ -3842,7 +3861,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="51"/>
-      <c r="G13" s="107"/>
+      <c r="G13" s="105"/>
       <c r="H13" s="39" t="s">
         <v>261</v>
       </c>
@@ -3901,7 +3920,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="51"/>
-      <c r="G14" s="107"/>
+      <c r="G14" s="105"/>
       <c r="H14" s="23"/>
       <c r="I14" s="36"/>
       <c r="J14" s="1"/>
@@ -3909,7 +3928,9 @@
       <c r="L14" s="36"/>
       <c r="M14" s="55"/>
       <c r="N14" s="35"/>
-      <c r="O14" s="56"/>
+      <c r="O14" s="56" t="s">
+        <v>51</v>
+      </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="54"/>
@@ -3917,7 +3938,9 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
-      <c r="W14" s="56"/>
+      <c r="W14" s="56" t="s">
+        <v>27</v>
+      </c>
       <c r="X14" s="35"/>
       <c r="Y14" s="47"/>
       <c r="Z14" s="36"/>
@@ -3948,7 +3971,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="51"/>
-      <c r="G15" s="107"/>
+      <c r="G15" s="105"/>
       <c r="H15" s="32" t="s">
         <v>37</v>
       </c>
@@ -3992,29 +4015,33 @@
       <c r="D16" s="44"/>
       <c r="E16" s="44"/>
       <c r="F16" s="51"/>
-      <c r="G16" s="107"/>
+      <c r="G16" s="105"/>
       <c r="H16" s="23"/>
       <c r="I16" s="34"/>
       <c r="J16" s="35"/>
-      <c r="K16" s="33"/>
+      <c r="K16" s="33" t="s">
+        <v>19</v>
+      </c>
       <c r="L16" s="36"/>
       <c r="M16" s="45"/>
       <c r="N16" s="1"/>
       <c r="O16" s="57"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-      <c r="R16" s="106" t="s">
+      <c r="R16" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="S16" s="107"/>
-      <c r="T16" s="107"/>
+      <c r="S16" s="105"/>
+      <c r="T16" s="105"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="58"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="49"/>
       <c r="Z16" s="36"/>
-      <c r="AA16" s="33"/>
+      <c r="AA16" s="33" t="s">
+        <v>8</v>
+      </c>
       <c r="AB16" s="35"/>
       <c r="AC16" s="37"/>
       <c r="AD16" s="23"/>
@@ -4041,7 +4068,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="51"/>
-      <c r="G17" s="107"/>
+      <c r="G17" s="105"/>
       <c r="H17" s="42" t="s">
         <v>42</v>
       </c>
@@ -4056,9 +4083,11 @@
       <c r="O17" s="57"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
-      <c r="R17" s="103"/>
-      <c r="S17" s="104"/>
-      <c r="T17" s="105"/>
+      <c r="R17" s="121" t="s">
+        <v>77</v>
+      </c>
+      <c r="S17" s="120"/>
+      <c r="T17" s="118"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="58"/>
@@ -4096,13 +4125,15 @@
         <v>1</v>
       </c>
       <c r="F18" s="51"/>
-      <c r="G18" s="107"/>
+      <c r="G18" s="105"/>
       <c r="H18" s="23"/>
       <c r="I18" s="36"/>
       <c r="J18" s="1"/>
       <c r="K18" s="55"/>
       <c r="L18" s="46"/>
-      <c r="M18" s="33"/>
+      <c r="M18" s="33" t="s">
+        <v>44</v>
+      </c>
       <c r="N18" s="1"/>
       <c r="O18" s="57"/>
       <c r="P18" s="1"/>
@@ -4111,7 +4142,9 @@
       <c r="V18" s="1"/>
       <c r="W18" s="58"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="33"/>
+      <c r="Y18" s="33" t="s">
+        <v>93</v>
+      </c>
       <c r="Z18" s="46"/>
       <c r="AA18" s="47"/>
       <c r="AB18" s="1"/>
@@ -4140,7 +4173,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="51"/>
-      <c r="G19" s="107"/>
+      <c r="G19" s="105"/>
       <c r="H19" s="42" t="s">
         <v>47</v>
       </c>
@@ -4192,27 +4225,35 @@
         <v>2</v>
       </c>
       <c r="F20" s="51"/>
-      <c r="G20" s="107"/>
+      <c r="G20" s="105"/>
       <c r="H20" s="23"/>
       <c r="I20" s="34"/>
       <c r="J20" s="35"/>
-      <c r="K20" s="33"/>
+      <c r="K20" s="33" t="s">
+        <v>44</v>
+      </c>
       <c r="L20" s="36"/>
       <c r="M20" s="52"/>
       <c r="N20" s="1"/>
       <c r="O20" s="57"/>
       <c r="P20" s="35"/>
-      <c r="Q20" s="108"/>
-      <c r="R20" s="105"/>
+      <c r="Q20" s="119" t="s">
+        <v>51</v>
+      </c>
+      <c r="R20" s="118"/>
       <c r="S20" s="61"/>
-      <c r="T20" s="108"/>
-      <c r="U20" s="105"/>
+      <c r="T20" s="119" t="s">
+        <v>77</v>
+      </c>
+      <c r="U20" s="118"/>
       <c r="V20" s="35"/>
       <c r="W20" s="58"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="52"/>
       <c r="Z20" s="36"/>
-      <c r="AA20" s="33"/>
+      <c r="AA20" s="33" t="s">
+        <v>93</v>
+      </c>
       <c r="AB20" s="35"/>
       <c r="AC20" s="37"/>
       <c r="AD20" s="23"/>
@@ -4239,7 +4280,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="51"/>
-      <c r="G21" s="107"/>
+      <c r="G21" s="105"/>
       <c r="H21" s="32" t="s">
         <v>53</v>
       </c>
@@ -4254,11 +4295,11 @@
       <c r="O21" s="57"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-      <c r="R21" s="109" t="s">
+      <c r="R21" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="S21" s="107"/>
-      <c r="T21" s="107"/>
+      <c r="S21" s="105"/>
+      <c r="T21" s="105"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="58"/>
@@ -4288,7 +4329,7 @@
       <c r="D22" s="44"/>
       <c r="E22" s="44"/>
       <c r="F22" s="51"/>
-      <c r="G22" s="107"/>
+      <c r="G22" s="105"/>
       <c r="H22" s="23"/>
       <c r="I22" s="36"/>
       <c r="J22" s="1"/>
@@ -4335,7 +4376,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="64"/>
-      <c r="G23" s="107"/>
+      <c r="G23" s="105"/>
       <c r="H23" s="32" t="s">
         <v>57</v>
       </c>
@@ -4390,11 +4431,13 @@
         <v>1</v>
       </c>
       <c r="F24" s="64"/>
-      <c r="G24" s="107"/>
+      <c r="G24" s="105"/>
       <c r="H24" s="23"/>
       <c r="I24" s="34"/>
       <c r="J24" s="35"/>
-      <c r="K24" s="33"/>
+      <c r="K24" s="33" t="s">
+        <v>98</v>
+      </c>
       <c r="L24" s="36"/>
       <c r="M24" s="52"/>
       <c r="N24" s="1"/>
@@ -4410,7 +4453,9 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="52"/>
       <c r="Z24" s="36"/>
-      <c r="AA24" s="33"/>
+      <c r="AA24" s="33" t="s">
+        <v>77</v>
+      </c>
       <c r="AB24" s="35"/>
       <c r="AC24" s="37"/>
       <c r="AD24" s="23"/>
@@ -4437,7 +4482,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="64"/>
-      <c r="G25" s="107"/>
+      <c r="G25" s="105"/>
       <c r="H25" s="42" t="s">
         <v>63</v>
       </c>
@@ -4452,11 +4497,11 @@
       <c r="O25" s="57"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-      <c r="R25" s="110" t="s">
+      <c r="R25" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="S25" s="107"/>
-      <c r="T25" s="107"/>
+      <c r="S25" s="105"/>
+      <c r="T25" s="105"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="58"/>
@@ -4494,25 +4539,33 @@
         <v>3</v>
       </c>
       <c r="F26" s="64"/>
-      <c r="G26" s="107"/>
+      <c r="G26" s="105"/>
       <c r="H26" s="23"/>
       <c r="I26" s="36"/>
       <c r="J26" s="1"/>
       <c r="K26" s="55"/>
       <c r="L26" s="46"/>
-      <c r="M26" s="33"/>
+      <c r="M26" s="33" t="s">
+        <v>60</v>
+      </c>
       <c r="N26" s="1"/>
       <c r="O26" s="57"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="105"/>
+      <c r="Q26" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="R26" s="118"/>
       <c r="S26" s="66"/>
-      <c r="T26" s="111"/>
-      <c r="U26" s="105"/>
+      <c r="T26" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="U26" s="118"/>
       <c r="V26" s="1"/>
       <c r="W26" s="58"/>
       <c r="X26" s="1"/>
-      <c r="Y26" s="33"/>
+      <c r="Y26" s="33" t="s">
+        <v>77</v>
+      </c>
       <c r="Z26" s="46"/>
       <c r="AA26" s="47"/>
       <c r="AB26" s="1"/>
@@ -4541,7 +4594,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="64"/>
-      <c r="G27" s="107"/>
+      <c r="G27" s="105"/>
       <c r="H27" s="42" t="s">
         <v>70</v>
       </c>
@@ -4556,7 +4609,7 @@
       <c r="O27" s="57"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-      <c r="S27" s="107"/>
+      <c r="S27" s="105"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="58"/>
@@ -4586,25 +4639,29 @@
       <c r="D28" s="44"/>
       <c r="E28" s="44"/>
       <c r="F28" s="51"/>
-      <c r="G28" s="107"/>
+      <c r="G28" s="105"/>
       <c r="H28" s="23"/>
       <c r="I28" s="34"/>
       <c r="J28" s="35"/>
-      <c r="K28" s="33"/>
+      <c r="K28" s="33" t="s">
+        <v>60</v>
+      </c>
       <c r="L28" s="36"/>
       <c r="M28" s="45"/>
       <c r="N28" s="1"/>
       <c r="O28" s="57"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-      <c r="S28" s="107"/>
+      <c r="S28" s="105"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="58"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="49"/>
       <c r="Z28" s="36"/>
-      <c r="AA28" s="33"/>
+      <c r="AA28" s="33" t="s">
+        <v>36</v>
+      </c>
       <c r="AB28" s="35"/>
       <c r="AC28" s="37"/>
       <c r="AD28" s="23"/>
@@ -4631,7 +4688,7 @@
         <v>6</v>
       </c>
       <c r="F29" s="51"/>
-      <c r="G29" s="107"/>
+      <c r="G29" s="105"/>
       <c r="H29" s="42" t="s">
         <v>74</v>
       </c>
@@ -4646,9 +4703,11 @@
       <c r="O29" s="57"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="104"/>
-      <c r="T29" s="105"/>
+      <c r="R29" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="S29" s="120"/>
+      <c r="T29" s="118"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="58"/>
@@ -4686,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="51"/>
-      <c r="G30" s="107"/>
+      <c r="G30" s="105"/>
       <c r="H30" s="23"/>
       <c r="I30" s="36"/>
       <c r="J30" s="1"/>
@@ -4694,17 +4753,21 @@
       <c r="L30" s="36"/>
       <c r="M30" s="55"/>
       <c r="N30" s="35"/>
-      <c r="O30" s="56"/>
+      <c r="O30" s="56" t="s">
+        <v>60</v>
+      </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-      <c r="R30" s="110" t="s">
+      <c r="R30" s="116" t="s">
         <v>78</v>
       </c>
-      <c r="S30" s="107"/>
-      <c r="T30" s="107"/>
+      <c r="S30" s="105"/>
+      <c r="T30" s="105"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
-      <c r="W30" s="56"/>
+      <c r="W30" s="56" t="s">
+        <v>77</v>
+      </c>
       <c r="X30" s="35"/>
       <c r="Y30" s="47"/>
       <c r="Z30" s="36"/>
@@ -4735,7 +4798,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="51"/>
-      <c r="G31" s="107"/>
+      <c r="G31" s="105"/>
       <c r="H31" s="42" t="s">
         <v>81</v>
       </c>
@@ -4790,29 +4853,33 @@
         <v>2</v>
       </c>
       <c r="F32" s="51"/>
-      <c r="G32" s="107"/>
+      <c r="G32" s="105"/>
       <c r="H32" s="23"/>
       <c r="I32" s="34"/>
       <c r="J32" s="35"/>
-      <c r="K32" s="33"/>
+      <c r="K32" s="33" t="s">
+        <v>28</v>
+      </c>
       <c r="L32" s="36"/>
       <c r="M32" s="40"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-      <c r="P32" s="122" t="s">
+      <c r="P32" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="Q32" s="107"/>
-      <c r="R32" s="107"/>
-      <c r="S32" s="107"/>
-      <c r="T32" s="107"/>
-      <c r="U32" s="107"/>
-      <c r="V32" s="107"/>
+      <c r="Q32" s="105"/>
+      <c r="R32" s="105"/>
+      <c r="S32" s="105"/>
+      <c r="T32" s="105"/>
+      <c r="U32" s="105"/>
+      <c r="V32" s="105"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="41"/>
       <c r="Z32" s="36"/>
-      <c r="AA32" s="33"/>
+      <c r="AA32" s="33" t="s">
+        <v>20</v>
+      </c>
       <c r="AB32" s="35"/>
       <c r="AC32" s="37"/>
       <c r="AD32" s="23"/>
@@ -4839,7 +4906,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="51"/>
-      <c r="G33" s="107"/>
+      <c r="G33" s="105"/>
       <c r="H33" s="39" t="s">
         <v>262</v>
       </c>
@@ -4851,13 +4918,13 @@
       <c r="L33" s="36"/>
       <c r="M33" s="40"/>
       <c r="N33" s="1"/>
-      <c r="P33" s="107"/>
-      <c r="Q33" s="107"/>
-      <c r="R33" s="107"/>
-      <c r="S33" s="107"/>
-      <c r="T33" s="107"/>
-      <c r="U33" s="107"/>
-      <c r="V33" s="107"/>
+      <c r="P33" s="105"/>
+      <c r="Q33" s="105"/>
+      <c r="R33" s="105"/>
+      <c r="S33" s="105"/>
+      <c r="T33" s="105"/>
+      <c r="U33" s="105"/>
+      <c r="V33" s="105"/>
       <c r="W33" s="69"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="41"/>
@@ -4885,25 +4952,29 @@
       <c r="D34" s="44"/>
       <c r="E34" s="44"/>
       <c r="F34" s="51"/>
-      <c r="G34" s="107"/>
+      <c r="G34" s="105"/>
       <c r="H34" s="23"/>
       <c r="I34" s="36"/>
       <c r="J34" s="1"/>
       <c r="K34" s="55"/>
       <c r="L34" s="46"/>
-      <c r="M34" s="33"/>
+      <c r="M34" s="33" t="s">
+        <v>59</v>
+      </c>
       <c r="N34" s="1"/>
       <c r="O34" s="69"/>
-      <c r="P34" s="107"/>
-      <c r="Q34" s="107"/>
-      <c r="R34" s="107"/>
-      <c r="S34" s="107"/>
-      <c r="T34" s="107"/>
-      <c r="U34" s="107"/>
-      <c r="V34" s="107"/>
+      <c r="P34" s="105"/>
+      <c r="Q34" s="105"/>
+      <c r="R34" s="105"/>
+      <c r="S34" s="105"/>
+      <c r="T34" s="105"/>
+      <c r="U34" s="105"/>
+      <c r="V34" s="105"/>
       <c r="W34" s="69"/>
       <c r="X34" s="1"/>
-      <c r="Y34" s="33"/>
+      <c r="Y34" s="33" t="s">
+        <v>92</v>
+      </c>
       <c r="Z34" s="46"/>
       <c r="AA34" s="47"/>
       <c r="AB34" s="1"/>
@@ -4932,7 +5003,7 @@
         <v>6</v>
       </c>
       <c r="F35" s="51"/>
-      <c r="G35" s="107"/>
+      <c r="G35" s="105"/>
       <c r="H35" s="32" t="s">
         <v>90</v>
       </c>
@@ -4945,13 +5016,13 @@
       <c r="M35" s="36"/>
       <c r="N35" s="1"/>
       <c r="O35" s="69"/>
-      <c r="P35" s="107"/>
-      <c r="Q35" s="107"/>
-      <c r="R35" s="107"/>
-      <c r="S35" s="107"/>
-      <c r="T35" s="107"/>
-      <c r="U35" s="107"/>
-      <c r="V35" s="107"/>
+      <c r="P35" s="105"/>
+      <c r="Q35" s="105"/>
+      <c r="R35" s="105"/>
+      <c r="S35" s="105"/>
+      <c r="T35" s="105"/>
+      <c r="U35" s="105"/>
+      <c r="V35" s="105"/>
       <c r="W35" s="69"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="36"/>
@@ -4987,27 +5058,31 @@
         <v>1</v>
       </c>
       <c r="F36" s="51"/>
-      <c r="G36" s="107"/>
+      <c r="G36" s="105"/>
       <c r="H36" s="23"/>
       <c r="I36" s="34"/>
       <c r="J36" s="35"/>
-      <c r="K36" s="33"/>
+      <c r="K36" s="33" t="s">
+        <v>59</v>
+      </c>
       <c r="L36" s="36"/>
       <c r="M36" s="36"/>
       <c r="N36" s="1"/>
       <c r="O36" s="69"/>
-      <c r="P36" s="107"/>
-      <c r="Q36" s="107"/>
-      <c r="R36" s="107"/>
-      <c r="S36" s="107"/>
-      <c r="T36" s="107"/>
-      <c r="U36" s="107"/>
-      <c r="V36" s="107"/>
+      <c r="P36" s="105"/>
+      <c r="Q36" s="105"/>
+      <c r="R36" s="105"/>
+      <c r="S36" s="105"/>
+      <c r="T36" s="105"/>
+      <c r="U36" s="105"/>
+      <c r="V36" s="105"/>
       <c r="W36" s="69"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="33"/>
+      <c r="AA36" s="33" t="s">
+        <v>92</v>
+      </c>
       <c r="AB36" s="35"/>
       <c r="AC36" s="37"/>
       <c r="AD36" s="23"/>
@@ -5034,7 +5109,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="51"/>
-      <c r="G37" s="107"/>
+      <c r="G37" s="105"/>
       <c r="H37" s="39" t="s">
         <v>263</v>
       </c>
@@ -5047,13 +5122,13 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="69"/>
-      <c r="P37" s="107"/>
-      <c r="Q37" s="107"/>
-      <c r="R37" s="107"/>
-      <c r="S37" s="107"/>
-      <c r="T37" s="107"/>
-      <c r="U37" s="107"/>
-      <c r="V37" s="107"/>
+      <c r="P37" s="105"/>
+      <c r="Q37" s="105"/>
+      <c r="R37" s="105"/>
+      <c r="S37" s="105"/>
+      <c r="T37" s="105"/>
+      <c r="U37" s="105"/>
+      <c r="V37" s="105"/>
       <c r="W37" s="69"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
@@ -5091,13 +5166,13 @@
       <c r="F38" s="51"/>
       <c r="H38" s="71"/>
       <c r="O38" s="69"/>
-      <c r="P38" s="107"/>
-      <c r="Q38" s="107"/>
-      <c r="R38" s="107"/>
-      <c r="S38" s="107"/>
-      <c r="T38" s="107"/>
-      <c r="U38" s="107"/>
-      <c r="V38" s="107"/>
+      <c r="P38" s="105"/>
+      <c r="Q38" s="105"/>
+      <c r="R38" s="105"/>
+      <c r="S38" s="105"/>
+      <c r="T38" s="105"/>
+      <c r="U38" s="105"/>
+      <c r="V38" s="105"/>
       <c r="W38" s="69"/>
       <c r="AD38" s="71"/>
       <c r="AE38" s="1"/>
@@ -6360,6 +6435,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="R21:T21"/>
     <mergeCell ref="G7:G37"/>
     <mergeCell ref="A1:AD1"/>
     <mergeCell ref="P32:V38"/>
@@ -6376,10 +6455,6 @@
     <mergeCell ref="R30:T30"/>
     <mergeCell ref="S27:S28"/>
     <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="R21:T21"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:A9 A12:A15 A18:A21 A24:A27 A30:A33 A36:A39">
     <cfRule type="expression" dxfId="49" priority="111" stopIfTrue="1">
@@ -6574,180 +6649,180 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="57">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA24" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA24">
       <formula1>$AC$23:$AC$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2K." sqref="I23" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2K." sqref="I23">
       <formula1>"🇵🇹 PORTUGAL,🇨🇩 REP. CONGO,🇺🇿 UZBEKISTÁN,🇨🇴 COLOMBIA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O30" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O30">
       <formula1>$M$26:$M$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O14" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O14">
       <formula1>$M$10:$M$18</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA32" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA32">
       <formula1>$AC$31:$AC$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K36" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K36">
       <formula1>$I$35:$I$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M26" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M26">
       <formula1>$K$24:$K$28</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2D." sqref="AC27" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2D." sqref="AC27">
       <formula1>"🇺🇸 ESTADOS UNIDOS,🇵🇾 PARAGUAY,🇦🇺 AUSTRALIA,🇹🇷 TURQUÍA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1G." sqref="I35" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1G." sqref="I35">
       <formula1>"🇧🇪 BÉLGICA,🇪🇬 EGIPTO,🇮🇷 IRÁN,🇳🇿 NUEVA ZELANDA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1H." sqref="I27" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1H." sqref="I27">
       <formula1>"🇪🇸 ESPAÑA,🇨🇻 CABO VERDE,🇸🇦 ARABIA SAUDÍ,🇺🇾 URUGUAY"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8">
       <formula1>$I$7:$I$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K12" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K12">
       <formula1>$I$11:$I$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W30" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W30">
       <formula1>$Y$26:$Y$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1K." sqref="AC35" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1K." sqref="AC35">
       <formula1>"🇵🇹 PORTUGAL,🇨🇩 REP. CONGO,🇺🇿 UZBEKISTÁN,🇨🇴 COLOMBIA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2C." sqref="I21" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2C." sqref="I21">
       <formula1>"🇧🇷 BRASIL,🇲🇦 MARRUECOS,🇭🇹 HAITÍ,🏴 ESCOCIA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1L." sqref="AC19" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1L." sqref="AC19">
       <formula1>"🇬🇧 INGLATERRA,🇭🇷 CROACIA,🇬🇭 GHANA,🇵🇦 PANAMÁ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W14" xr:uid="{00000000-0002-0000-0000-000010000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W14">
       <formula1>$Y$10:$Y$18</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA16" xr:uid="{00000000-0002-0000-0000-000011000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA16">
       <formula1>$AC$15:$AC$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y34" xr:uid="{00000000-0002-0000-0000-000012000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y34">
       <formula1>$AA$32:$AA$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1I." sqref="I11" xr:uid="{00000000-0002-0000-0000-000013000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1I." sqref="I11">
       <formula1>"🇫🇷 FRANCIA,🇸🇳 SENEGAL,🇮🇶 IRAK,🇳🇴 NORUEGA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1E." sqref="I7" xr:uid="{00000000-0002-0000-0000-000014000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1E." sqref="I7">
       <formula1>"🇩🇪 ALEMANIA,🇨🇼 CURAZAO,🇨🇮 COSTA DE MARFIL,🇪🇨 ECUADOR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T20 T26" xr:uid="{00000000-0002-0000-0000-000015000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T20 T26">
       <formula1>$W$14:$W$30</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA28" xr:uid="{00000000-0002-0000-0000-000016000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA28">
       <formula1>$AC$27:$AC$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M10" xr:uid="{00000000-0002-0000-0000-000017000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M10">
       <formula1>$K$8:$K$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M18" xr:uid="{00000000-0002-0000-0000-000018000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M18">
       <formula1>$K$16:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1J." sqref="AC23" xr:uid="{00000000-0002-0000-0000-000019000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1J." sqref="AC23">
       <formula1>"🇦🇷 ARGENTINA,🇩🇿 ARGELIA,🇦🇹 AUSTRIA,🇯🇴 JORDANIA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1D." sqref="I31" xr:uid="{00000000-0002-0000-0000-00001A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1D." sqref="I31">
       <formula1>"🇺🇸 ESTADOS UNIDOS,🇵🇾 PARAGUAY,🇦🇺 AUSTRALIA,🇹🇷 TURQUÍA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA36" xr:uid="{00000000-0002-0000-0000-00001B000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA36">
       <formula1>$AC$35:$AC$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2A." sqref="I15 AC15" xr:uid="{00000000-0002-0000-0000-00001C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2A." sqref="I15 AC15">
       <formula1>"🇲🇽 MÉXICO,🇿🇦 SUDÁFRICA,🇰🇷 COREA DEL SUR,🇨🇿 REP. CHECA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2B." sqref="I17" xr:uid="{00000000-0002-0000-0000-00001D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2B." sqref="I17">
       <formula1>"🇨🇦 CANADÁ,🇧🇦 BOSNIA Y HERZEGOVINA,🇶🇦 QATAR,🇨🇭 SUIZA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I9 I13 AC17 AC21 I33 AC33 I37 AC37" xr:uid="{00000000-0002-0000-0000-00001E000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I9 I13 AC17 AC21 I33 AC33 I37 AC37">
       <formula1>$AH$11:$AH$58</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q20 Q26" xr:uid="{00000000-0002-0000-0000-00001F000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q20 Q26">
       <formula1>$O$14:$O$30</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K20" xr:uid="{00000000-0002-0000-0000-000020000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K20">
       <formula1>$I$19:$I$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Click and enter a value from the list of items" sqref="AC25" xr:uid="{00000000-0002-0000-0000-000021000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Click and enter a value from the list of items" sqref="AC25">
       <formula1>"🇪🇸 ESPAÑA,🇨🇻 CABO VERDE,🇸🇦 ARABIA SAUDÍ,🇺🇾 URUGUAY"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2I." sqref="AC13" xr:uid="{00000000-0002-0000-0000-000022000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2I." sqref="AC13">
       <formula1>"🇫🇷 FRANCIA,🇸🇳 SENEGAL,🇮🇶 IRAK,🇳🇴 NORUEGA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2E." sqref="AC11" xr:uid="{00000000-0002-0000-0000-000023000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2E." sqref="AC11">
       <formula1>"🇩🇪 ALEMANIA,🇨🇼 CURAZAO,🇨🇮 COSTA DE MARFIL,🇪🇨 ECUADOR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona la posición del equipo: 1, 2, 3 o 4." sqref="B6:B9 E6:E9 AG6:AI9 B12:B15 E12:E15 B18:B21 E18:E21 B24:B27 E24:E27 B30:B33 E30:E33 B36:B39 E36:E39" xr:uid="{00000000-0002-0000-0000-000024000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona la posición del equipo: 1, 2, 3 o 4." sqref="B6:B9 E6:E9 AG6:AI9 B12:B15 E12:E15 B18:B21 E18:E21 B24:B27 E24:E27 B30:B33 E30:E33 B36:B39 E36:E39">
       <formula1>"1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y26" xr:uid="{00000000-0002-0000-0000-000025000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y26">
       <formula1>$AA$24:$AA$28</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R29" xr:uid="{00000000-0002-0000-0000-000026000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R29">
       <formula1>$Q$26:$U$26</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K32" xr:uid="{00000000-0002-0000-0000-000027000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K32">
       <formula1>$I$31:$I$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M34" xr:uid="{00000000-0002-0000-0000-000028000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M34">
       <formula1>$K$32:$K$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K16" xr:uid="{00000000-0002-0000-0000-000029000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K16">
       <formula1>$I$15:$I$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2L." sqref="I25" xr:uid="{00000000-0002-0000-0000-00002A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2L." sqref="I25">
       <formula1>"🇬🇧 INGLATERRA,🇭🇷 CROACIA,🇬🇭 GHANA,🇵🇦 PANAMÁ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA8" xr:uid="{00000000-0002-0000-0000-00002B000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA8">
       <formula1>$AC$7:$AC$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1B." sqref="AC31" xr:uid="{00000000-0002-0000-0000-00002C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1B." sqref="AC31">
       <formula1>"🇨🇦 CANADÁ,🇧🇦 BOSNIA Y HERZEGOVINA,🇶🇦 QATAR,🇨🇭 SUIZA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1F." sqref="I19" xr:uid="{00000000-0002-0000-0000-00002D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1F." sqref="I19">
       <formula1>"🇳🇱 HOLANDA,🇯🇵 JAPÓN,🇸🇪 SUECIA,🇹🇳 TÚNEZ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1C." sqref="AC7" xr:uid="{00000000-0002-0000-0000-00002E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 1C." sqref="AC7">
       <formula1>"🇧🇷 BRASIL,🇲🇦 MARRUECOS,🇭🇹 HAITÍ,🏴 ESCOCIA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2F." sqref="AC9" xr:uid="{00000000-0002-0000-0000-00002F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2F." sqref="AC9">
       <formula1>"🇳🇱 HOLANDA,🇯🇵 JAPÓN,🇸🇪 SUECIA,🇹🇳 TÚNEZ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K28" xr:uid="{00000000-0002-0000-0000-000030000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K28">
       <formula1>$I$27:$I$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2J." sqref="I29" xr:uid="{00000000-0002-0000-0000-000031000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2J." sqref="I29">
       <formula1>"🇦🇷 ARGENTINA,🇩🇿 ARGELIA,🇦🇹 AUSTRIA,🇯🇴 JORDANIA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA20" xr:uid="{00000000-0002-0000-0000-000032000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA20">
       <formula1>$AC$19:$AC$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y10" xr:uid="{00000000-0002-0000-0000-000033000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y10">
       <formula1>$AA$8:$AA$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y18" xr:uid="{00000000-0002-0000-0000-000034000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y18">
       <formula1>$AA$16:$AA$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K24" xr:uid="{00000000-0002-0000-0000-000035000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K24">
       <formula1>$I$23:$I$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA12" xr:uid="{00000000-0002-0000-0000-000036000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA12">
       <formula1>$AC$11:$AC$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R17" xr:uid="{00000000-0002-0000-0000-000037000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R17">
       <formula1>$Q$20:$U$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2G." sqref="AC29" xr:uid="{00000000-0002-0000-0000-000038000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Selecciona el equipo para 2G." sqref="AC29">
       <formula1>"🇧🇪 BÉLGICA,🇪🇬 EGIPTO,🇮🇷 IRÁN,🇳🇿 NUEVA ZELANDA"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AA2" r:id="rId1" xr:uid="{83E4356C-709A-6448-B682-C3B9C82FD648}"/>
+    <hyperlink ref="AA2" r:id="rId1"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -6757,8 +6832,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6788,23 +6863,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
       <c r="P1" s="86"/>
       <c r="Q1" s="86"/>
       <c r="R1" s="86"/>
@@ -6814,31 +6889,31 @@
       <c r="V1" s="88"/>
     </row>
     <row r="2" spans="1:22" ht="77.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="125"/>
-      <c r="C2" s="127" t="s">
+      <c r="B2" s="140"/>
+      <c r="C2" s="149" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="125"/>
+      <c r="D2" s="140"/>
       <c r="E2" s="129" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="131" t="s">
+      <c r="F2" s="153" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="116"/>
+      <c r="G2" s="112"/>
       <c r="H2" s="89"/>
       <c r="I2" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="123" t="s">
+      <c r="J2" s="139" t="s">
         <v>106</v>
       </c>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="125"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="140"/>
       <c r="N2" s="90" t="s">
         <v>107</v>
       </c>
@@ -6856,27 +6931,27 @@
       <c r="V2" s="88"/>
     </row>
     <row r="3" spans="1:22" ht="77.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="139" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="125"/>
-      <c r="C3" s="133">
+      <c r="B3" s="140"/>
+      <c r="C3" s="155">
         <v>10</v>
       </c>
-      <c r="D3" s="125"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="132"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="152"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="154"/>
       <c r="H3" s="89"/>
       <c r="I3" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="126" t="s">
+      <c r="J3" s="156" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="125"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="140"/>
       <c r="N3" s="91" t="s">
         <v>111</v>
       </c>
@@ -6895,22 +6970,22 @@
       <c r="A4" s="129" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="150"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="132"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="154"/>
       <c r="H4" s="89"/>
       <c r="I4" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="126" t="s">
+      <c r="J4" s="156" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="125"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="140"/>
       <c r="N4" s="91" t="s">
         <v>114</v>
       </c>
@@ -6926,23 +7001,23 @@
       <c r="V4" s="88"/>
     </row>
     <row r="5" spans="1:22" ht="77.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="117"/>
-      <c r="B5" s="119"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="132"/>
+      <c r="A5" s="113"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="154"/>
       <c r="H5" s="89"/>
       <c r="I5" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="156" t="s">
         <v>115</v>
       </c>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="125"/>
+      <c r="K5" s="150"/>
+      <c r="L5" s="150"/>
+      <c r="M5" s="140"/>
       <c r="N5" s="91" t="s">
         <v>116</v>
       </c>
@@ -6958,27 +7033,27 @@
       <c r="V5" s="88"/>
     </row>
     <row r="6" spans="1:22" ht="77.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="125"/>
-      <c r="C6" s="138" t="s">
+      <c r="B6" s="140"/>
+      <c r="C6" s="141" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="125"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="119"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="115"/>
       <c r="H6" s="89"/>
       <c r="I6" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="126" t="s">
+      <c r="J6" s="156" t="s">
         <v>119</v>
       </c>
-      <c r="K6" s="124"/>
-      <c r="L6" s="124"/>
-      <c r="M6" s="125"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="150"/>
+      <c r="M6" s="140"/>
       <c r="N6" s="91" t="s">
         <v>120</v>
       </c>
@@ -7005,12 +7080,12 @@
       <c r="I7" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="126" t="s">
+      <c r="J7" s="156" t="s">
         <v>121</v>
       </c>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="125"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="140"/>
       <c r="N7" s="91" t="s">
         <v>122</v>
       </c>
@@ -7035,12 +7110,12 @@
       <c r="G8" s="89"/>
       <c r="H8" s="89"/>
       <c r="I8" s="91"/>
-      <c r="J8" s="127" t="s">
+      <c r="J8" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="K8" s="124"/>
-      <c r="L8" s="124"/>
-      <c r="M8" s="125"/>
+      <c r="K8" s="150"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="140"/>
       <c r="N8" s="92" t="s">
         <v>124</v>
       </c>
@@ -7081,21 +7156,21 @@
       </c>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="139" t="s">
+    <row r="10" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="140"/>
-      <c r="C10" s="140"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="141"/>
+      <c r="B10" s="143"/>
+      <c r="C10" s="143"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="143"/>
+      <c r="L10" s="144"/>
       <c r="M10" s="93"/>
       <c r="N10" s="93"/>
       <c r="O10" s="93"/>
@@ -7107,31 +7182,31 @@
       <c r="U10" s="94"/>
       <c r="V10" s="95"/>
     </row>
-    <row r="11" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="142" t="s">
+    <row r="11" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="145" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="135"/>
-      <c r="C11" s="143" t="s">
+      <c r="B11" s="132"/>
+      <c r="C11" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="135"/>
-      <c r="E11" s="144" t="s">
+      <c r="D11" s="132"/>
+      <c r="E11" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="135"/>
-      <c r="G11" s="145" t="s">
+      <c r="F11" s="132"/>
+      <c r="G11" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="135"/>
-      <c r="I11" s="134" t="s">
+      <c r="H11" s="132"/>
+      <c r="I11" s="137" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="135"/>
-      <c r="K11" s="136" t="s">
+      <c r="J11" s="132"/>
+      <c r="K11" s="138" t="s">
         <v>41</v>
       </c>
-      <c r="L11" s="137"/>
+      <c r="L11" s="125"/>
       <c r="M11" s="93"/>
       <c r="N11" s="93"/>
       <c r="O11" s="93"/>
@@ -7143,7 +7218,7 @@
       <c r="U11" s="94"/>
       <c r="V11" s="95"/>
     </row>
-    <row r="12" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="96" t="s">
         <v>126</v>
       </c>
@@ -7191,7 +7266,7 @@
       <c r="U12" s="94"/>
       <c r="V12" s="95"/>
     </row>
-    <row r="13" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="99" t="s">
         <v>128</v>
       </c>
@@ -7239,7 +7314,7 @@
       <c r="U13" s="94"/>
       <c r="V13" s="95"/>
     </row>
-    <row r="14" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="99" t="s">
         <v>140</v>
       </c>
@@ -7287,7 +7362,7 @@
       <c r="U14" s="94"/>
       <c r="V14" s="95"/>
     </row>
-    <row r="15" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="99" t="s">
         <v>152</v>
       </c>
@@ -7335,7 +7410,7 @@
       <c r="U15" s="94"/>
       <c r="V15" s="95"/>
     </row>
-    <row r="16" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="99" t="s">
         <v>164</v>
       </c>
@@ -7383,7 +7458,7 @@
       <c r="U16" s="94"/>
       <c r="V16" s="95"/>
     </row>
-    <row r="17" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="99" t="s">
         <v>176</v>
       </c>
@@ -7431,7 +7506,7 @@
       <c r="U17" s="94"/>
       <c r="V17" s="95"/>
     </row>
-    <row r="18" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="99" t="s">
         <v>176</v>
       </c>
@@ -7479,7 +7554,7 @@
       <c r="U18" s="94"/>
       <c r="V18" s="95"/>
     </row>
-    <row r="19" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="93"/>
       <c r="B19" s="93"/>
       <c r="C19" s="93"/>
@@ -7503,31 +7578,31 @@
       <c r="U19" s="94"/>
       <c r="V19" s="95"/>
     </row>
-    <row r="20" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="151" t="s">
+    <row r="20" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="135"/>
-      <c r="C20" s="152" t="s">
+      <c r="B20" s="132"/>
+      <c r="C20" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="135"/>
-      <c r="E20" s="153" t="s">
+      <c r="D20" s="132"/>
+      <c r="E20" s="134" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="135"/>
-      <c r="G20" s="154" t="s">
+      <c r="F20" s="132"/>
+      <c r="G20" s="135" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="135"/>
-      <c r="I20" s="155" t="s">
+      <c r="H20" s="132"/>
+      <c r="I20" s="136" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="135"/>
-      <c r="K20" s="146" t="s">
+      <c r="J20" s="132"/>
+      <c r="K20" s="124" t="s">
         <v>89</v>
       </c>
-      <c r="L20" s="137"/>
+      <c r="L20" s="125"/>
       <c r="M20" s="93"/>
       <c r="N20" s="93"/>
       <c r="O20" s="93"/>
@@ -7539,7 +7614,7 @@
       <c r="U20" s="94"/>
       <c r="V20" s="95"/>
     </row>
-    <row r="21" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="96" t="s">
         <v>126</v>
       </c>
@@ -7587,7 +7662,7 @@
       <c r="U21" s="94"/>
       <c r="V21" s="95"/>
     </row>
-    <row r="22" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="99" t="s">
         <v>194</v>
       </c>
@@ -7635,7 +7710,7 @@
       <c r="U22" s="94"/>
       <c r="V22" s="95"/>
     </row>
-    <row r="23" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="99" t="s">
         <v>206</v>
       </c>
@@ -7683,7 +7758,7 @@
       <c r="U23" s="94"/>
       <c r="V23" s="95"/>
     </row>
-    <row r="24" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="99" t="s">
         <v>218</v>
       </c>
@@ -7731,7 +7806,7 @@
       <c r="U24" s="94"/>
       <c r="V24" s="95"/>
     </row>
-    <row r="25" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="99" t="s">
         <v>230</v>
       </c>
@@ -7779,7 +7854,7 @@
       <c r="U25" s="94"/>
       <c r="V25" s="95"/>
     </row>
-    <row r="26" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="99" t="s">
         <v>242</v>
       </c>
@@ -7827,7 +7902,7 @@
       <c r="U26" s="94"/>
       <c r="V26" s="95"/>
     </row>
-    <row r="27" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="99" t="s">
         <v>242</v>
       </c>
@@ -7875,19 +7950,19 @@
       <c r="U27" s="94"/>
       <c r="V27" s="95"/>
     </row>
-    <row r="28" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="147"/>
-      <c r="B28" s="148"/>
-      <c r="C28" s="148"/>
-      <c r="D28" s="148"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="148"/>
-      <c r="G28" s="148"/>
-      <c r="H28" s="148"/>
-      <c r="I28" s="148"/>
-      <c r="J28" s="148"/>
-      <c r="K28" s="148"/>
-      <c r="L28" s="149"/>
+    <row r="28" spans="1:22" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="126"/>
+      <c r="B28" s="127"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="127"/>
+      <c r="K28" s="127"/>
+      <c r="L28" s="128"/>
       <c r="M28" s="93"/>
       <c r="N28" s="93"/>
       <c r="O28" s="93"/>
@@ -7901,6 +7976,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="F2:G6"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="J7:M7"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A4:B5"/>
@@ -7917,22 +8008,6 @@
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="F2:G6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="J7:M7"/>
   </mergeCells>
   <conditionalFormatting sqref="U1:U28">
     <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
@@ -7943,7 +8018,7 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C6" r:id="rId1"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
